--- a/public/downloads/holorecall-italian-v5.xlsx
+++ b/public/downloads/holorecall-italian-v5.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="213">
   <si>
     <t>key</t>
   </si>
@@ -26,7 +26,7 @@
     <t>format_version</t>
   </si>
   <si>
-    <t>5</t>
+    <t>9</t>
   </si>
   <si>
     <t>content_only</t>
@@ -56,6 +56,12 @@
     <t>anki_source</t>
   </si>
   <si>
+    <t>cover_media</t>
+  </si>
+  <si>
+    <t>study_art_policy</t>
+  </si>
+  <si>
     <t>italian-essentials</t>
   </si>
   <si>
@@ -117,6 +123,27 @@
   </si>
   <si>
     <t>sibling_group_id</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>choices</t>
+  </si>
+  <si>
+    <t>answer_label</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>presentation</t>
   </si>
   <si>
     <t>it-limone</t>
@@ -617,6 +644,9 @@
   </si>
   <si>
     <t>texture</t>
+  </si>
+  <si>
+    <t>design_schema</t>
   </si>
   <si>
     <t>asset_id</t>
@@ -1062,13 +1092,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
+    <col min="1" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,32 +1120,44 @@
       <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1123,1068 +1165,1425 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="20" width="18" customWidth="1"/>
+    <col min="1" max="27" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>16</v>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="2" t="s">
+    <row r="6" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>16</v>
+      <c r="K6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="2" t="s">
+    <row r="7" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>16</v>
+      <c r="K7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="2" t="s">
+    <row r="8" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>16</v>
+      <c r="K8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="2" t="s">
+    <row r="9" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>16</v>
+      <c r="K12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="13" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>16</v>
+      <c r="D13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>16</v>
+    <row r="14" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>16</v>
+    <row r="15" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>16</v>
+    <row r="16" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T17"/>
+  <autoFilter ref="A1:AA17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2192,84 +2591,87 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="18" customWidth="1"/>
     <col min="13" max="14" width="21" customWidth="1"/>
-    <col min="15" max="22" width="18" customWidth="1"/>
+    <col min="15" max="23" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V1"/>
+  <autoFilter ref="A1:W1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2285,31 +2687,31 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
